--- a/iconlist.xlsx
+++ b/iconlist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{987A4F15-275D-44E8-AA7D-54317BF02903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0416841-B2BA-4C1E-A8E9-FB79813AD41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{473F3770-BEB5-4B5F-BE7A-0A28FC568EC5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/96MCblue.png</t>
   </si>
@@ -36,9 +36,6 @@
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/96MCgreen.png</t>
   </si>
   <si>
-    <t>{9901,9904,9908,0010,0111,0201}</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/96MCgreen_chu.png</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuaero_green.png</t>
   </si>
   <si>
-    <t>{1002,1003,1004,1005,1101,1102,1103,1104,1201,1202,1301,1302,1303}</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuj_completelygreen.png</t>
   </si>
   <si>
@@ -78,9 +72,6 @@
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuj_green.png</t>
   </si>
   <si>
-    <t>{0506,0508,0704,0705,0706,0707,0708,0710,0711,0712,0713,0715,0716,0717,0902,0904,0905,0906,0907}</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuJ_lightblue.png</t>
   </si>
   <si>
@@ -175,13 +166,33 @@
   </si>
   <si>
     <t>{1601}</t>
+  </si>
+  <si>
+    <t>{1001,1002,1003,1004,1005,1101,1102,1103,1104,1201,1202,1203,1301,1302,1303}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0109,9901,9904,9908,0010,0111,0201}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/midhiorange.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{702}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0903,0506,0508,0704,0705,0706,0707,0708,0710,0711,0712,0713,0715,0716,0717,0902,0904,0905,0906,0907}</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,6 +203,15 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -215,17 +235,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -538,8 +565,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3FEE6F-0F7B-48C1-BDF3-85C854F9DB56}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="82.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
@@ -554,195 +584,206 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="1" t="s">
         <v>49</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="A26" r:id="rId1" xr:uid="{996A13E9-D0CC-4BC6-BF47-3270ED109574}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/iconlist.xlsx
+++ b/iconlist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0416841-B2BA-4C1E-A8E9-FB79813AD41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010AA2D1-2F6B-46EB-8E8D-47D91F4CA6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{473F3770-BEB5-4B5F-BE7A-0A28FC568EC5}"/>
   </bookViews>
@@ -25,166 +25,182 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+  <si>
+    <t>{0009}</t>
+  </si>
+  <si>
+    <t>{0101,0102,0104}</t>
+  </si>
+  <si>
+    <t>{0006}</t>
+  </si>
+  <si>
+    <t>{1901,1902,1903,1904,1905,1906,2001}</t>
+  </si>
+  <si>
+    <t>{1105}</t>
+  </si>
+  <si>
+    <t>{0901}</t>
+  </si>
+  <si>
+    <t>{0504}</t>
+  </si>
+  <si>
+    <t>{0709}</t>
+  </si>
+  <si>
+    <t>{0507}</t>
+  </si>
+  <si>
+    <t>{0505,0509}</t>
+  </si>
+  <si>
+    <t>{0503}</t>
+  </si>
+  <si>
+    <t>{0702,0703}</t>
+  </si>
+  <si>
+    <t>{1702,2303,2401}</t>
+  </si>
+  <si>
+    <t>{2502,2503,2504,2505}</t>
+  </si>
+  <si>
+    <t>{2201,2202]</t>
+  </si>
+  <si>
+    <t>{1502}</t>
+  </si>
+  <si>
+    <t>{1401}</t>
+  </si>
+  <si>
+    <t>{1402,1503}</t>
+  </si>
+  <si>
+    <t>{1501}</t>
+  </si>
+  <si>
+    <t>{1403}</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_white.png</t>
+  </si>
+  <si>
+    <t>{1701}</t>
+  </si>
+  <si>
+    <t>{1601}</t>
+  </si>
+  <si>
+    <t>{1001,1002,1003,1004,1005,1101,1102,1103,1104,1201,1202,1203,1301,1302,1303}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0109,9901,9904,9908,0010,0111,0201}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/midhiorange.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{702}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0903,0506,0508,0704,0705,0706,0707,0708,0710,0711,0712,0713,0715,0716,0717,0902,0904,0905,0906,0907}</t>
+    <phoneticPr fontId="1"/>
+  </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/96MCblue.png</t>
-  </si>
-  <si>
-    <t>{0009}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/96MCgreen.png</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/96MCgreen_chu.png</t>
-  </si>
-  <si>
-    <t>{0101,0102,0104}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/chabo_green.png</t>
-  </si>
-  <si>
-    <t>{0006}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/hiace.png</t>
-  </si>
-  <si>
-    <t>{1901,1902,1903,1904,1905,1906,2001}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuaero_blue.png</t>
-  </si>
-  <si>
-    <t>{1105}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuaero_green.png</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuj_completelygreen.png</t>
-  </si>
-  <si>
-    <t>{0901}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuj_green.png</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuJ_lightblue.png</t>
-  </si>
-  <si>
-    <t>{0504}</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuJ_purple.png</t>
-  </si>
-  <si>
-    <t>{0709}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuJ_red.png</t>
-  </si>
-  <si>
-    <t>{0507}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuj_white.png</t>
-  </si>
-  <si>
-    <t>{0505,0509}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuJ_yellow.png</t>
-  </si>
-  <si>
-    <t>{0503}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/midhitwon_orange.png</t>
-  </si>
-  <si>
-    <t>{0702,0703}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/midhitwon_red.png</t>
-  </si>
-  <si>
-    <t>{1702,2303,2401}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/poncho.png</t>
-  </si>
-  <si>
-    <t>{2502,2503,2504,2505}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/rosa_grenn.png</t>
-  </si>
-  <si>
-    <t>{2201,2202]</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_green.png</t>
-  </si>
-  <si>
-    <t>{1502}</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_greenwhite.png</t>
-  </si>
-  <si>
-    <t>{1401}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_lightblue.png</t>
-  </si>
-  <si>
-    <t>{1402,1503}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_orange.png</t>
-  </si>
-  <si>
-    <t>{1501}</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_red.png</t>
-  </si>
-  <si>
-    <t>{1403}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_white.png</t>
-  </si>
-  <si>
-    <t>{1701}</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/sinJ_white.png</t>
-  </si>
-  <si>
-    <t>{1601}</t>
-  </si>
-  <si>
-    <t>{1001,1002,1003,1004,1005,1101,1102,1103,1104,1201,1202,1203,1301,1302,1303}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0109,9901,9904,9908,0010,0111,0201}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/midhiorange.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{702}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0903,0506,0508,0704,0705,0706,0707,0708,0710,0711,0712,0713,0715,0716,0717,0902,0904,0905,0906,0907}</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -243,11 +259,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -569,220 +588,245 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="82.25" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
+      <c r="B23" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
+        <v>20</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" t="s">
-        <v>46</v>
+      <c r="A25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" t="s">
-        <v>50</v>
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="A26" r:id="rId1" xr:uid="{996A13E9-D0CC-4BC6-BF47-3270ED109574}"/>
+    <hyperlink ref="A1" r:id="rId2" xr:uid="{41C01009-0E8C-4FD4-BE15-D227577F6AC9}"/>
+    <hyperlink ref="A2" r:id="rId3" xr:uid="{8A426529-BD72-4C36-A355-3EFA428E2D82}"/>
+    <hyperlink ref="A3" r:id="rId4" xr:uid="{7E135AD9-3A69-45A9-8224-9FAABAFD842E}"/>
+    <hyperlink ref="A4" r:id="rId5" xr:uid="{AE3837C5-8AD1-43A9-A0E5-C3988356BE45}"/>
+    <hyperlink ref="A5" r:id="rId6" xr:uid="{FD77E7E8-6866-4FC8-A464-BAFD70EE16F2}"/>
+    <hyperlink ref="A6" r:id="rId7" xr:uid="{F7CE46A2-5B50-425D-B54F-0348F2E6EE30}"/>
+    <hyperlink ref="A7" r:id="rId8" xr:uid="{FFEE9A58-5937-428E-AF78-FE3F0A83CF86}"/>
+    <hyperlink ref="A8" r:id="rId9" xr:uid="{93EECB1B-85C8-4B8F-A251-2C023B7A6B9D}"/>
+    <hyperlink ref="A9" r:id="rId10" xr:uid="{41BFFEAC-E4F9-4385-B3E0-3BF1E0025F64}"/>
+    <hyperlink ref="A10" r:id="rId11" xr:uid="{1D82132D-682D-4D35-8B8F-F4E65F150D7B}"/>
+    <hyperlink ref="A11" r:id="rId12" xr:uid="{63E9A2AE-6CF5-4AE3-8CDC-5209A43B933C}"/>
+    <hyperlink ref="A12" r:id="rId13" xr:uid="{EAE79362-DCBC-4645-89F6-6FA50F46CAB9}"/>
+    <hyperlink ref="A13" r:id="rId14" xr:uid="{32FDB16E-0C5C-4C39-8B79-1661CBD4FCA2}"/>
+    <hyperlink ref="A14" r:id="rId15" xr:uid="{9AA03A2F-829B-4FCB-95BF-85164881408C}"/>
+    <hyperlink ref="A15" r:id="rId16" xr:uid="{9AC2EAB5-9379-47C5-A07C-A13DB45568A5}"/>
+    <hyperlink ref="A16" r:id="rId17" xr:uid="{C2467F0F-39F2-4D84-8CFF-2E1282CD7E63}"/>
+    <hyperlink ref="A17" r:id="rId18" xr:uid="{4FFB1BF0-613C-4BB0-815E-FD006AB45C6C}"/>
+    <hyperlink ref="A18" r:id="rId19" xr:uid="{C67C81D9-AC17-4AF3-8127-3D35AFDC2ED0}"/>
+    <hyperlink ref="A19" r:id="rId20" xr:uid="{6DABC128-F34E-4D3F-9169-3EF4ED3F05E6}"/>
+    <hyperlink ref="A20" r:id="rId21" xr:uid="{CDED4EF7-6D3C-4257-A0E0-914322A93A50}"/>
+    <hyperlink ref="A21" r:id="rId22" xr:uid="{112610CC-623B-42ED-B768-809F7EDF2248}"/>
+    <hyperlink ref="A22" r:id="rId23" xr:uid="{D1F5BCA0-E490-43E6-A34F-669BEDC3E988}"/>
+    <hyperlink ref="A23" r:id="rId24" xr:uid="{5C63351B-60E0-412E-96DC-0FAC8459975E}"/>
+    <hyperlink ref="A25" r:id="rId25" xr:uid="{685F96EA-E65B-4469-BE14-B798868E4113}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iconlist.xlsx
+++ b/iconlist.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Downloads\ファイル_000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010AA2D1-2F6B-46EB-8E8D-47D91F4CA6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9C474A-53FF-46D1-AD0C-1956BB169417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{473F3770-BEB5-4B5F-BE7A-0A28FC568EC5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>{0009}</t>
   </si>
@@ -69,138 +69,147 @@
     <t>{2502,2503,2504,2505}</t>
   </si>
   <si>
+    <t>{1502}</t>
+  </si>
+  <si>
+    <t>{1401}</t>
+  </si>
+  <si>
+    <t>{1402,1503}</t>
+  </si>
+  <si>
+    <t>{1501}</t>
+  </si>
+  <si>
+    <t>{1403}</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_white.png</t>
+  </si>
+  <si>
+    <t>{1701}</t>
+  </si>
+  <si>
+    <t>{1601}</t>
+  </si>
+  <si>
+    <t>{1001,1002,1003,1004,1005,1101,1102,1103,1104,1201,1202,1203,1301,1302,1303}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0109,9901,9904,9908,0010,0111,0201}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/midhiorange.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{702}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/96MCblue.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/96MCgreen.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/96MCgreen_chu.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/chabo_green.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/hiace.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuaero_blue.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuaero_green.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuj_completelygreen.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuj_green.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuJ_lightblue.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuJ_red.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuj_white.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuJ_yellow.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/midhitwon_orange.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/midhitwon_red.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/poncho.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/rosa_grenn.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_green.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_lightblue.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_orange.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_white.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/sinJ_white.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/EV.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{ＥＶバス}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>{2201,2202]</t>
-  </si>
-  <si>
-    <t>{1502}</t>
-  </si>
-  <si>
-    <t>{1401}</t>
-  </si>
-  <si>
-    <t>{1402,1503}</t>
-  </si>
-  <si>
-    <t>{1501}</t>
-  </si>
-  <si>
-    <t>{1403}</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_white.png</t>
-  </si>
-  <si>
-    <t>{1701}</t>
-  </si>
-  <si>
-    <t>{1601}</t>
-  </si>
-  <si>
-    <t>{1001,1002,1003,1004,1005,1101,1102,1103,1104,1201,1202,1203,1301,1302,1303}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0109,9901,9904,9908,0010,0111,0201}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/midhiorange.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{702}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0903,0506,0508,0704,0705,0706,0707,0708,0710,0711,0712,0713,0715,0716,0717,0902,0904,0905,0906,0907}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/96MCblue.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/96MCgreen.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/96MCgreen_chu.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/chabo_green.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/hiace.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuaero_blue.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuaero_green.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuj_completelygreen.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuj_green.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuJ_lightblue.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuJ_red.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuj_white.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/kyuJ_yellow.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/midhitwon_orange.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/midhitwon_red.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/poncho.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/rosa_grenn.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_green.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_lightblue.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_orange.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/shinaero_white.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/sakuraps1134/ktqcity-busnavi/main/sinJ_white.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{2302,2501,0903,0506,0508,0704,0705,0706,0707,0708,0710,0711,0712,0713,0715,0716,0717,0902,0904,0905,0906,0907}</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -259,14 +268,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -584,219 +590,226 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3FEE6F-0F7B-48C1-BDF3-85C854F9DB56}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="82.25" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>14</v>
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
         <v>20</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>22</v>
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>26</v>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -827,6 +840,7 @@
     <hyperlink ref="A22" r:id="rId23" xr:uid="{D1F5BCA0-E490-43E6-A34F-669BEDC3E988}"/>
     <hyperlink ref="A23" r:id="rId24" xr:uid="{5C63351B-60E0-412E-96DC-0FAC8459975E}"/>
     <hyperlink ref="A25" r:id="rId25" xr:uid="{685F96EA-E65B-4469-BE14-B798868E4113}"/>
+    <hyperlink ref="A27" r:id="rId26" xr:uid="{DCC2580E-FD57-4816-BEA7-EEBB2AFF3767}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iconlist.xlsx
+++ b/iconlist.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Downloads\ファイル_000\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9C474A-53FF-46D1-AD0C-1956BB169417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E19578-D4DE-4241-806F-58F10A42A637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{473F3770-BEB5-4B5F-BE7A-0A28FC568EC5}"/>
   </bookViews>
@@ -36,9 +36,6 @@
     <t>{0006}</t>
   </si>
   <si>
-    <t>{1901,1902,1903,1904,1905,1906,2001}</t>
-  </si>
-  <si>
     <t>{1105}</t>
   </si>
   <si>
@@ -210,6 +207,10 @@
   </si>
   <si>
     <t>{2302,2501,0903,0506,0508,0704,0705,0706,0707,0708,0710,0711,0712,0713,0715,0716,0717,0902,0904,0905,0906,0907}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{1901(ﾊｲｴｰｽ),1902(ﾊｲｴｰｽ),1903(ﾊｲｴｰｽ),1904(ﾊｲｴｰｽ),1905(ﾊｲｴｰｽ),1906(ﾊｲｴｰｽ),2001(ﾊｲｴｰｽ)}</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -598,7 +599,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -606,15 +607,15 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -622,7 +623,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -630,186 +631,186 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
         <v>19</v>
-      </c>
-      <c r="B24" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
         <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s">
         <v>48</v>
-      </c>
-      <c r="B27" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
